--- a/artfynd/A 30486-2024 artfynd.xlsx
+++ b/artfynd/A 30486-2024 artfynd.xlsx
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Sterner, Agnes  Blomgren</t>
+          <t>Britta Sterner, Agnes Blomgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 30486-2024 artfynd.xlsx
+++ b/artfynd/A 30486-2024 artfynd.xlsx
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Sterner, Agnes Blomgren</t>
+          <t>Britta Sterner, Agnes  Blomgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 30486-2024 artfynd.xlsx
+++ b/artfynd/A 30486-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2307855</v>
+        <v>119625544</v>
       </c>
       <c r="B2" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,51 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Drolvägen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522219.1351885367</v>
+        <v>522267</v>
       </c>
       <c r="R2" t="n">
-        <v>6951116.937054338</v>
+        <v>6951136</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-06-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>fuktig kalbarrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -806,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119625544</v>
+        <v>127830705</v>
       </c>
       <c r="B3" t="n">
-        <v>90334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57903</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>102110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Drolvägen, Jmt</t>
+          <t>Bensjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522267</v>
+        <v>522175</v>
       </c>
       <c r="R3" t="n">
-        <v>6951136</v>
+        <v>6951079</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>06:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>06:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,62 +867,75 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124547062</v>
+        <v>2307855</v>
       </c>
       <c r="B4" t="n">
-        <v>57433</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102110</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bensjön, Jmt</t>
+          <t>Drolvägen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522175</v>
+        <v>522219</v>
       </c>
       <c r="R4" t="n">
-        <v>6951079</v>
+        <v>6951117</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2008-06-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2008-06-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,22 +979,23 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>fuktig kalbarrskog</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Sterner, Agnes  Blomgren</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30486-2024 artfynd.xlsx
+++ b/artfynd/A 30486-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625544</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830705</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,8 +1011,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2307855</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>